--- a/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
+++ b/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,6 +1319,870 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FTP 服务已安装，状态为 Running</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>请在【服务】中禁用 FTP 服务</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FTP服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TCP 21 端口未监听</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FTP端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无FTP防火墙入站规则</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FTP防火墙规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FTP客户端功能已启用</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>请在系统功能中取消 FTP 客户端 勾选</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FTP客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>检测到 4 个网卡</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>确认网卡状态是否符合预期</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>网卡信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>网卡名称: 以太网, 状态: Up, 描述: Realtek PCIe GbE Family Controller</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet1, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>网卡名称: VirtualBox Host-Only Network, 状态: Up, 描述: VirtualBox Host-Only Ethernet Adapter</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet8, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet8</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>已获取网卡IP配置信息</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>网卡IP配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>网卡: 以太网, IPv4: 172.16.1.20, DNS: 218.108.248.200</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet1, IPv4: 192.168.119.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>网卡: VirtualBox Host-Only Network, IPv4: 192.168.56.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet8, IPv4: 192.168.137.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>未检测到无线网卡</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>无线网卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>端口 22 被封禁</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>端口 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>端口 23 被封禁</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>端口 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>端口 135 被封禁</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>端口 135</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>端口 137 被封禁</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>端口 137</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>端口 138 被封禁</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>端口 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>端口 139 被封禁</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>端口 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>端口 445 被封禁</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>端口 445</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>端口 455 被封禁</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>端口 455</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>端口 3389 被封禁</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>端口 3389</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>端口 4899 未封禁</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>请封禁该端口</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>端口 4899</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IPv6 未完全禁用 (DisabledComponents = )</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>请设置 DisabledComponents = 255</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IPv6</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>最新更新：KB5051989，日期：03/02/2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>请核查补丁内容</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>更新补丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">net accounts 输出: Force user logoff how long after time expires?:       Never Minimum password age (days):                          0 Maximum password age (days):                          42 Minimum password length:                              8 Length of password history maintained:                None Lockout threshold:                                    10 Lockout duration (minutes):                           10 Lockout observation window (minutes):                 10 Computer role:                                        WORKSTATION The command completed successfully. </t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>将最长密码有效期设置为不超过 90 天</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>密码策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>已禁用</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Guest 用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>未完全禁用 (NoDriveTypeAutoRun = 221)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>请修改为 255</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>U盘自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>版本：134.0.6998.118</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>请确认是否为最新版本</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-03-28 16:53:12</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>超时时间：600 秒</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>锁屏策略</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
+++ b/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-03-28 16:37:35</t>
+          <t>2025-03-31 08:21:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025-03-28 16:53:12</t>
+          <t>2025-03-31 08:22:18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">

--- a/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
+++ b/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,6 +2183,870 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FTP 服务已安装，状态为 Running</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>请在【服务】中禁用 FTP 服务</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FTP服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TCP 21 端口未监听</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FTP端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>无FTP防火墙入站规则</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FTP防火墙规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FTP客户端功能已启用</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>请在系统功能中取消 FTP 客户端 勾选</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>FTP客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>检测到 4 个网卡</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>确认网卡状态是否符合预期</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>网卡信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>网卡名称: 以太网, 状态: Up, 描述: Realtek PCIe GbE Family Controller</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet1, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>网卡名称: VirtualBox Host-Only Network, 状态: Up, 描述: VirtualBox Host-Only Ethernet Adapter</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet8, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet8</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>已获取网卡IP配置信息</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>网卡IP配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>网卡: 以太网, IPv4: 172.16.1.20, DNS: 218.108.248.200</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet1, IPv4: 192.168.119.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>网卡: VirtualBox Host-Only Network, IPv4: 192.168.56.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet8, IPv4: 192.168.137.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>未检测到无线网卡</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>无线网卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>端口 22 被封禁</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>端口 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>端口 23 被封禁</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>端口 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>端口 135 被封禁</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>端口 135</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>端口 137 被封禁</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>端口 137</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>端口 138 被封禁</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>端口 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>端口 139 被封禁</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>端口 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>端口 445 被封禁</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>端口 445</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>端口 455 被封禁</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>端口 455</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>端口 3389 被封禁</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>端口 3389</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>端口 4899 未封禁</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>请封禁该端口</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>端口 4899</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>IPv6 未完全禁用 (DisabledComponents = )</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>请设置 DisabledComponents = 255</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IPv6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>最新更新：KB5051989，日期：03/02/2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>请核查补丁内容</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>更新补丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">net accounts 输出: Force user logoff how long after time expires?:       Never Minimum password age (days):                          0 Maximum password age (days):                          42 Minimum password length:                              8 Length of password history maintained:                None Lockout threshold:                                    10 Lockout duration (minutes):                           10 Lockout observation window (minutes):                 10 Computer role:                                        WORKSTATION The command completed successfully. </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>将最长密码有效期设置为不超过 90 天</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>密码策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>已禁用</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Guest 用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>未完全禁用 (NoDriveTypeAutoRun = 221)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>请修改为 255</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>U盘自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>版本：134.0.6998.178</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>请确认是否为最新版本</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025-04-01 14:05:35</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>超时时间：600 秒</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>锁屏策略</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
+++ b/BaseLineCheck/SecurityCheck_v5检查程序/带授权+服务的批量检查版本/Monitor/summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,6 +1319,2598 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FTP 服务已安装，状态为 Running</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>请在【服务】中禁用 FTP 服务</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FTP服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TCP 21 端口未监听</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FTP端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无FTP防火墙入站规则</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FTP防火墙规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FTP客户端功能已启用</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>请在系统功能中取消 FTP 客户端 勾选</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FTP客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>检测到 4 个网卡</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>确认网卡状态是否符合预期</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>网卡信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>网卡名称: 以太网, 状态: Up, 描述: Realtek PCIe GbE Family Controller</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet1, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>网卡名称: VirtualBox Host-Only Network, 状态: Up, 描述: VirtualBox Host-Only Ethernet Adapter</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet8, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet8</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>已获取网卡IP配置信息</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>网卡IP配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>网卡: 以太网, IPv4: 172.16.1.20, DNS: 218.108.248.200</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet1, IPv4: 192.168.119.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>网卡: VirtualBox Host-Only Network, IPv4: 192.168.56.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet8, IPv4: 192.168.137.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>未检测到无线网卡</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>无线网卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>端口 22 被封禁</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>端口 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>端口 23 被封禁</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>端口 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>端口 135 被封禁</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>端口 135</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>端口 137 被封禁</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>端口 137</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>端口 138 被封禁</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>端口 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>端口 139 被封禁</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>端口 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>端口 445 被封禁</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>端口 445</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>端口 455 被封禁</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>端口 455</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>端口 3389 被封禁</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>端口 3389</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>端口 4899 未封禁</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>请封禁该端口</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>端口 4899</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IPv6 未完全禁用 (DisabledComponents = )</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>请设置 DisabledComponents = 255</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IPv6</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>最新更新：KB5051989，日期：03/02/2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>请核查补丁内容</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>更新补丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">net accounts 输出: Force user logoff how long after time expires?:       Never Minimum password age (days):                          0 Maximum password age (days):                          42 Minimum password length:                              8 Length of password history maintained:                None Lockout threshold:                                    10 Lockout duration (minutes):                           10 Lockout observation window (minutes):                 10 Computer role:                                        WORKSTATION The command completed successfully. </t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>将最长密码有效期设置为不超过 90 天</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>密码策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>已禁用</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Guest 用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>未完全禁用 (NoDriveTypeAutoRun = 221)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>请修改为 255</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>U盘自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>版本：134.0.6998.178</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>请确认是否为最新版本</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:39:12</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>超时时间：600 秒</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>锁屏策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FTP 服务已安装，状态为 Running</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>请在【服务】中禁用 FTP 服务</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FTP服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TCP 21 端口未监听</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FTP端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>无FTP防火墙入站规则</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FTP防火墙规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FTP客户端功能已启用</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>请在系统功能中取消 FTP 客户端 勾选</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>FTP客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>检测到 4 个网卡</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>确认网卡状态是否符合预期</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>网卡信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>网卡名称: 以太网, 状态: Up, 描述: Realtek PCIe GbE Family Controller</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet1, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>网卡名称: VirtualBox Host-Only Network, 状态: Up, 描述: VirtualBox Host-Only Ethernet Adapter</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet8, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet8</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>已获取网卡IP配置信息</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>网卡IP配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>网卡: 以太网, IPv4: 172.16.1.20, DNS: 218.108.248.200</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet1, IPv4: 192.168.119.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>网卡: VirtualBox Host-Only Network, IPv4: 192.168.56.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet8, IPv4: 192.168.137.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>未检测到无线网卡</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>无线网卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>端口 22 被封禁</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>端口 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>端口 23 被封禁</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>端口 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>端口 135 被封禁</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>端口 135</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>端口 137 被封禁</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>端口 137</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>端口 138 被封禁</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>端口 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>端口 139 被封禁</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>端口 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>端口 445 被封禁</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>端口 445</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>端口 455 被封禁</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>端口 455</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>端口 3389 被封禁</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>端口 3389</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>端口 4899 未封禁</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>请封禁该端口</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>端口 4899</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>IPv6 未完全禁用 (DisabledComponents = )</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>请设置 DisabledComponents = 255</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IPv6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>最新更新：KB5051989，日期：03/02/2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>请核查补丁内容</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>更新补丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">net accounts 输出: Force user logoff how long after time expires?:       Never Minimum password age (days):                          0 Maximum password age (days):                          42 Minimum password length:                              8 Length of password history maintained:                None Lockout threshold:                                    10 Lockout duration (minutes):                           10 Lockout observation window (minutes):                 10 Computer role:                                        WORKSTATION The command completed successfully. </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>将最长密码有效期设置为不超过 90 天</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>密码策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>已禁用</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Guest 用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>未完全禁用 (NoDriveTypeAutoRun = 221)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>请修改为 255</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>U盘自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>版本：134.0.6998.178</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>请确认是否为最新版本</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025-04-01 15:41:05</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>超时时间：600 秒</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>锁屏策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FTP 服务已安装，状态为 Running</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>请在【服务】中禁用 FTP 服务</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>FTP服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TCP 21 端口未监听</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>FTP端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>无FTP防火墙入站规则</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>FTP防火墙规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>FTP客户端功能已启用</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>请在系统功能中取消 FTP 客户端 勾选</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>FTP客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>检测到 4 个网卡</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>确认网卡状态是否符合预期</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>网卡信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>网卡名称: 以太网, 状态: Up, 描述: Realtek PCIe GbE Family Controller</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet1, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>网卡名称: VirtualBox Host-Only Network, 状态: Up, 描述: VirtualBox Host-Only Ethernet Adapter</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>网卡名称: VMware Network Adapter VMnet8, 状态: Up, 描述: VMware Virtual Ethernet Adapter for VMnet8</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>网卡详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>已获取网卡IP配置信息</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>网卡IP配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>网卡: 以太网, IPv4: 172.16.1.20, DNS: 218.108.248.200</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet1, IPv4: 192.168.119.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>网卡: VirtualBox Host-Only Network, IPv4: 192.168.56.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>网卡: VMware Network Adapter VMnet8, IPv4: 192.168.137.1, DNS: fec0:0:0:ffff::1,fec0:0:0:ffff::2,fec0:0:0:ffff::3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>网卡配置详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>未检测到无线网卡</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>无线网卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>端口 22 被封禁</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>端口 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>端口 23 被封禁</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>端口 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>端口 135 被封禁</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>端口 135</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>端口 137 被封禁</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>端口 137</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>端口 138 被封禁</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>端口 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>端口 139 被封禁</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>端口 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>端口 445 被封禁</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>端口 445</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>端口 455 被封禁</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>端口 455</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>端口 3389 被封禁</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>端口 3389</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>端口 4899 未封禁</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>请封禁该端口</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>端口 4899</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>IPv6 未完全禁用 (DisabledComponents = )</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>请设置 DisabledComponents = 255</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>IPv6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>最新更新：KB5051989，日期：03/02/2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>请核查补丁内容</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>更新补丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">net accounts 输出: Force user logoff how long after time expires?:       Never Minimum password age (days):                          0 Maximum password age (days):                          42 Minimum password length:                              8 Length of password history maintained:                None Lockout threshold:                                    10 Lockout duration (minutes):                           10 Lockout observation window (minutes):                 10 Computer role:                                        WORKSTATION The command completed successfully. </t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>将最长密码有效期设置为不超过 90 天</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>密码策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>已禁用</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Guest 用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>未完全禁用 (NoDriveTypeAutoRun = 221)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>请修改为 255</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>U盘自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>版本：134.0.6998.178</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>请确认是否为最新版本</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025-04-01 16:00:21</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>超时时间：600 秒</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>锁屏策略</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
